--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.99779859954795</v>
+        <v>3.412142272426541</v>
       </c>
       <c r="D2" t="n">
-        <v>20.69294722170292</v>
+        <v>3.362603923526724</v>
       </c>
       <c r="E2" t="n">
-        <v>8.972502143717152</v>
+        <v>1.458031598354037</v>
       </c>
       <c r="F2" t="n">
-        <v>8.972446541564953</v>
+        <v>1.458022563004305</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.716549614108522</v>
+        <v>0.7664393122926348</v>
       </c>
       <c r="D3" t="n">
-        <v>5.176984322658001</v>
+        <v>0.8412599524319252</v>
       </c>
       <c r="E3" t="n">
-        <v>8.972502143717152</v>
+        <v>1.458031598354037</v>
       </c>
       <c r="F3" t="n">
-        <v>8.972446541564953</v>
+        <v>1.458022563004305</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.47302930199562</v>
+        <v>4.301867261574289</v>
       </c>
       <c r="D4" t="n">
-        <v>26.50758505498543</v>
+        <v>4.307482571435132</v>
       </c>
       <c r="E4" t="n">
-        <v>8.972502143717152</v>
+        <v>1.458031598354037</v>
       </c>
       <c r="F4" t="n">
-        <v>8.972446541564953</v>
+        <v>1.458022563004305</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.810587677274288</v>
+        <v>1.269220497557072</v>
       </c>
       <c r="D5" t="n">
-        <v>7.778706475922643</v>
+        <v>1.26403980233743</v>
       </c>
       <c r="E5" t="n">
-        <v>8.972502143717152</v>
+        <v>1.458031598354037</v>
       </c>
       <c r="F5" t="n">
-        <v>8.972446541564953</v>
+        <v>1.458022563004305</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.157744512236675</v>
+        <v>0.8381334832384596</v>
       </c>
       <c r="D6" t="n">
-        <v>4.488154913113692</v>
+        <v>0.729325173380975</v>
       </c>
       <c r="E6" t="n">
-        <v>8.972502143717152</v>
+        <v>1.458031598354037</v>
       </c>
       <c r="F6" t="n">
-        <v>8.972446541564953</v>
+        <v>1.458022563004305</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
